--- a/paper_traning_lay0x0/sinais_lay0x0_gestao_2026-08-16.xlsx
+++ b/paper_traning_lay0x0/sinais_lay0x0_gestao_2026-08-16.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/paper_traning_lay0x0/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_698D1C8D57096754FFDA3D11595ED87656CD9E3E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E8170F9-6630-417B-AC7A-CADA27FC534B}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_698D1C8D57096754FFDA3D11595ED87656CD9E3E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{066AECA0-600F-4AF9-98EF-03DBD4F71352}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -417,6 +417,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1822,13 +1826,13 @@
       </c>
       <c r="L25" t="str">
         <f t="shared" si="0"/>
-        <v>GREEN</v>
+        <v>RED</v>
       </c>
       <c r="N25" t="s">
         <v>20</v>
       </c>
       <c r="O25">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
